--- a/ns_playwright_automation/test_data/ShippingData_NS.xlsx
+++ b/ns_playwright_automation/test_data/ShippingData_NS.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\struts_playwright_automation\ns_playwright_automation\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16FBDB3D-B4C5-4C27-B83E-56BBC747D1E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9161F8F6-80E2-4033-8D3C-4E83855DA772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="590" xr2:uid="{82038ABE-7B8C-4146-9485-918A215A8E15}"/>
   </bookViews>
@@ -1662,6 +1662,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1065429E-9165-42A9-9DDC-E545596C17BE}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:CC119"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2079,7 +2080,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="3" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
         <v>74</v>
       </c>
@@ -2180,7 +2181,7 @@
       <c r="BV3" s="2"/>
       <c r="BW3" s="2"/>
     </row>
-    <row r="4" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
         <v>76</v>
       </c>
@@ -2281,7 +2282,7 @@
       <c r="BV4" s="2"/>
       <c r="BW4" s="2"/>
     </row>
-    <row r="5" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
         <v>78</v>
       </c>
@@ -2417,7 +2418,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
         <v>79</v>
       </c>
@@ -2513,7 +2514,7 @@
       <c r="BV6" s="2"/>
       <c r="BW6" s="2"/>
     </row>
-    <row r="7" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
         <v>80</v>
       </c>
@@ -2609,7 +2610,7 @@
       <c r="BV7" s="2"/>
       <c r="BW7" s="2"/>
     </row>
-    <row r="8" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
         <v>81</v>
       </c>
@@ -2705,7 +2706,7 @@
       <c r="BV8" s="2"/>
       <c r="BW8" s="2"/>
     </row>
-    <row r="9" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
         <v>82</v>
       </c>
@@ -2801,7 +2802,7 @@
       <c r="BV9" s="2"/>
       <c r="BW9" s="2"/>
     </row>
-    <row r="10" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
         <v>83</v>
       </c>
@@ -2897,7 +2898,7 @@
       <c r="BV10" s="2"/>
       <c r="BW10" s="2"/>
     </row>
-    <row r="11" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
         <v>84</v>
       </c>
@@ -2993,7 +2994,7 @@
       <c r="BV11" s="2"/>
       <c r="BW11" s="2"/>
     </row>
-    <row r="12" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
         <v>85</v>
       </c>
@@ -3089,7 +3090,7 @@
       <c r="BV12" s="2"/>
       <c r="BW12" s="2"/>
     </row>
-    <row r="13" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
         <v>86</v>
       </c>
@@ -3185,7 +3186,7 @@
       <c r="BV13" s="2"/>
       <c r="BW13" s="2"/>
     </row>
-    <row r="14" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
         <v>99</v>
       </c>
@@ -3286,7 +3287,7 @@
       <c r="BV14" s="1"/>
       <c r="BW14" s="1"/>
     </row>
-    <row r="15" spans="1:81" ht="72" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:81" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
         <v>100</v>
       </c>
@@ -3429,7 +3430,7 @@
       <c r="BV15" s="1"/>
       <c r="BW15" s="1"/>
     </row>
-    <row r="16" spans="1:81" ht="72" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:81" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" s="6" t="s">
         <v>114</v>
       </c>
@@ -3574,7 +3575,7 @@
       <c r="BV16" s="1"/>
       <c r="BW16" s="1"/>
     </row>
-    <row r="17" spans="1:75" ht="72" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:75" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" s="6" t="s">
         <v>222</v>
       </c>
@@ -3721,7 +3722,7 @@
       <c r="BV17" s="1"/>
       <c r="BW17" s="1"/>
     </row>
-    <row r="18" spans="1:75" ht="72" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:75" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" s="6" t="s">
         <v>251</v>
       </c>
@@ -3870,7 +3871,7 @@
       <c r="BV18" s="1"/>
       <c r="BW18" s="1"/>
     </row>
-    <row r="19" spans="1:75" ht="72" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:75" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" s="6" t="s">
         <v>115</v>
       </c>
@@ -4017,7 +4018,7 @@
       <c r="BV19" s="1"/>
       <c r="BW19" s="1"/>
     </row>
-    <row r="20" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" s="6" t="s">
         <v>116</v>
       </c>
@@ -4126,7 +4127,7 @@
       <c r="BV20" s="1"/>
       <c r="BW20" s="1"/>
     </row>
-    <row r="21" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" s="6" t="s">
         <v>117</v>
       </c>
@@ -4237,7 +4238,7 @@
       <c r="BV21" s="1"/>
       <c r="BW21" s="1"/>
     </row>
-    <row r="22" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" s="6" t="s">
         <v>118</v>
       </c>
@@ -4348,7 +4349,7 @@
       <c r="BV22" s="1"/>
       <c r="BW22" s="1"/>
     </row>
-    <row r="23" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="6" t="s">
         <v>119</v>
       </c>
@@ -4455,7 +4456,7 @@
       <c r="BV23" s="1"/>
       <c r="BW23" s="1"/>
     </row>
-    <row r="24" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="6" t="s">
         <v>120</v>
       </c>
@@ -4564,7 +4565,7 @@
       <c r="BV24" s="1"/>
       <c r="BW24" s="1"/>
     </row>
-    <row r="25" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="6" t="s">
         <v>121</v>
       </c>
@@ -4669,7 +4670,7 @@
       <c r="BV25" s="1"/>
       <c r="BW25" s="1"/>
     </row>
-    <row r="26" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="6" t="s">
         <v>279</v>
       </c>
@@ -4776,7 +4777,7 @@
       <c r="BV26" s="1"/>
       <c r="BW26" s="1"/>
     </row>
-    <row r="27" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="6" t="s">
         <v>87</v>
       </c>
@@ -4875,7 +4876,7 @@
       <c r="BV27" s="2"/>
       <c r="BW27" s="2"/>
     </row>
-    <row r="28" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="6" t="s">
         <v>88</v>
       </c>
@@ -4976,7 +4977,7 @@
       <c r="BV28" s="2"/>
       <c r="BW28" s="2"/>
     </row>
-    <row r="29" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="6" t="s">
         <v>89</v>
       </c>
@@ -5077,7 +5078,7 @@
       <c r="BV29" s="2"/>
       <c r="BW29" s="2"/>
     </row>
-    <row r="30" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" s="6" t="s">
         <v>90</v>
       </c>
@@ -5178,7 +5179,7 @@
       <c r="BV30" s="2"/>
       <c r="BW30" s="2"/>
     </row>
-    <row r="31" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" s="6" t="s">
         <v>92</v>
       </c>
@@ -5277,7 +5278,7 @@
       <c r="BV31" s="2"/>
       <c r="BW31" s="2"/>
     </row>
-    <row r="32" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" s="6" t="s">
         <v>93</v>
       </c>
@@ -5373,7 +5374,7 @@
       <c r="BV32" s="2"/>
       <c r="BW32" s="2"/>
     </row>
-    <row r="33" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" s="6" t="s">
         <v>94</v>
       </c>
@@ -5475,7 +5476,7 @@
       <c r="BV33" s="2"/>
       <c r="BW33" s="2"/>
     </row>
-    <row r="34" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" s="6" t="s">
         <v>158</v>
       </c>
@@ -5576,7 +5577,7 @@
       <c r="BV34" s="1"/>
       <c r="BW34" s="1"/>
     </row>
-    <row r="35" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" s="6" t="s">
         <v>161</v>
       </c>
@@ -5719,7 +5720,7 @@
       <c r="BV35" s="1"/>
       <c r="BW35" s="1"/>
     </row>
-    <row r="36" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" s="6" t="s">
         <v>234</v>
       </c>
@@ -5866,7 +5867,7 @@
       <c r="BV36" s="1"/>
       <c r="BW36" s="1"/>
     </row>
-    <row r="37" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" s="6" t="s">
         <v>162</v>
       </c>
@@ -6011,7 +6012,7 @@
       <c r="BV37" s="1"/>
       <c r="BW37" s="1"/>
     </row>
-    <row r="38" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" s="6" t="s">
         <v>233</v>
       </c>
@@ -6160,7 +6161,7 @@
       <c r="BV38" s="1"/>
       <c r="BW38" s="1"/>
     </row>
-    <row r="39" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" s="6" t="s">
         <v>163</v>
       </c>
@@ -6307,7 +6308,7 @@
       <c r="BV39" s="1"/>
       <c r="BW39" s="1"/>
     </row>
-    <row r="40" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="6" t="s">
         <v>164</v>
       </c>
@@ -6416,7 +6417,7 @@
       <c r="BV40" s="1"/>
       <c r="BW40" s="1"/>
     </row>
-    <row r="41" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="6" t="s">
         <v>165</v>
       </c>
@@ -6527,7 +6528,7 @@
       <c r="BV41" s="1"/>
       <c r="BW41" s="1"/>
     </row>
-    <row r="42" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="6" t="s">
         <v>166</v>
       </c>
@@ -6632,7 +6633,7 @@
       <c r="BV42" s="1"/>
       <c r="BW42" s="1"/>
     </row>
-    <row r="43" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="6" t="s">
         <v>278</v>
       </c>
@@ -6834,7 +6835,7 @@
       <c r="BV44" s="2"/>
       <c r="BW44" s="2"/>
     </row>
-    <row r="45" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="6" t="s">
         <v>123</v>
       </c>
@@ -6931,7 +6932,7 @@
       <c r="BV45" s="2"/>
       <c r="BW45" s="2"/>
     </row>
-    <row r="46" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="6" t="s">
         <v>124</v>
       </c>
@@ -7028,7 +7029,7 @@
       <c r="BV46" s="2"/>
       <c r="BW46" s="2"/>
     </row>
-    <row r="47" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="6" t="s">
         <v>125</v>
       </c>
@@ -7125,7 +7126,7 @@
       <c r="BV47" s="2"/>
       <c r="BW47" s="2"/>
     </row>
-    <row r="48" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="6" t="s">
         <v>126</v>
       </c>
@@ -7220,7 +7221,7 @@
       <c r="BV48" s="2"/>
       <c r="BW48" s="2"/>
     </row>
-    <row r="49" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="6" t="s">
         <v>160</v>
       </c>
@@ -7317,7 +7318,7 @@
       <c r="BV49" s="1"/>
       <c r="BW49" s="1"/>
     </row>
-    <row r="50" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="6" t="s">
         <v>128</v>
       </c>
@@ -7424,7 +7425,7 @@
       <c r="BV50" s="1"/>
       <c r="BW50" s="1"/>
     </row>
-    <row r="51" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="6" t="s">
         <v>129</v>
       </c>
@@ -7533,7 +7534,7 @@
       <c r="BV51" s="1"/>
       <c r="BW51" s="1"/>
     </row>
-    <row r="52" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="6" t="s">
         <v>130</v>
       </c>
@@ -7642,7 +7643,7 @@
       <c r="BV52" s="1"/>
       <c r="BW52" s="1"/>
     </row>
-    <row r="53" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="6" t="s">
         <v>141</v>
       </c>
@@ -7745,7 +7746,7 @@
       <c r="BV53" s="2"/>
       <c r="BW53" s="2"/>
     </row>
-    <row r="54" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="6" t="s">
         <v>142</v>
       </c>
@@ -7850,7 +7851,7 @@
       <c r="BV54" s="2"/>
       <c r="BW54" s="2"/>
     </row>
-    <row r="55" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="6" t="s">
         <v>143</v>
       </c>
@@ -7953,7 +7954,7 @@
       <c r="BV55" s="2"/>
       <c r="BW55" s="2"/>
     </row>
-    <row r="56" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="6" t="s">
         <v>145</v>
       </c>
@@ -8054,7 +8055,7 @@
       <c r="BV56" s="1"/>
       <c r="BW56" s="1"/>
     </row>
-    <row r="57" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="6" t="s">
         <v>147</v>
       </c>
@@ -8157,7 +8158,7 @@
       <c r="BV57" s="1"/>
       <c r="BW57" s="1"/>
     </row>
-    <row r="58" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="6" t="s">
         <v>223</v>
       </c>
@@ -8262,7 +8263,7 @@
       <c r="BV58" s="1"/>
       <c r="BW58" s="1"/>
     </row>
-    <row r="59" spans="1:75" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:75" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="6" t="s">
         <v>224</v>
       </c>
@@ -8369,7 +8370,7 @@
       <c r="BV59" s="1"/>
       <c r="BW59" s="1"/>
     </row>
-    <row r="60" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="6" t="s">
         <v>146</v>
       </c>
@@ -8569,7 +8570,7 @@
       <c r="BV61" s="2"/>
       <c r="BW61" s="2"/>
     </row>
-    <row r="62" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
         <v>156</v>
       </c>
@@ -8666,7 +8667,7 @@
       <c r="BV62" s="2"/>
       <c r="BW62" s="2"/>
     </row>
-    <row r="63" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="6" t="s">
         <v>157</v>
       </c>
@@ -8763,7 +8764,7 @@
       <c r="BV63" s="2"/>
       <c r="BW63" s="2"/>
     </row>
-    <row r="64" spans="1:75" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:75" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="6" t="s">
         <v>159</v>
       </c>
@@ -8860,7 +8861,7 @@
       <c r="BV64" s="1"/>
       <c r="BW64" s="1"/>
     </row>
-    <row r="65" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="6" t="s">
         <v>148</v>
       </c>
@@ -8969,7 +8970,7 @@
       <c r="BV65" s="1"/>
       <c r="BW65" s="1"/>
     </row>
-    <row r="66" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="6" t="s">
         <v>280</v>
       </c>
@@ -9080,7 +9081,7 @@
       <c r="BV66" s="1"/>
       <c r="BW66" s="1"/>
     </row>
-    <row r="67" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="6" t="s">
         <v>149</v>
       </c>
@@ -9191,7 +9192,7 @@
       <c r="BV67" s="1"/>
       <c r="BW67" s="1"/>
     </row>
-    <row r="68" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="6" t="s">
         <v>281</v>
       </c>
@@ -9306,7 +9307,7 @@
       <c r="BV68" s="1"/>
       <c r="BW68" s="1"/>
     </row>
-    <row r="69" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="6" t="s">
         <v>150</v>
       </c>
@@ -9419,7 +9420,7 @@
       <c r="BV69" s="1"/>
       <c r="BW69" s="1"/>
     </row>
-    <row r="70" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="6" t="s">
         <v>185</v>
       </c>
@@ -9638,7 +9639,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="72" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="6" t="s">
         <v>187</v>
       </c>
@@ -9773,7 +9774,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="73" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="6" t="s">
         <v>252</v>
       </c>
@@ -9908,7 +9909,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="74" spans="1:81" ht="72" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:81" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="6" t="s">
         <v>253</v>
       </c>
@@ -10085,7 +10086,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="75" spans="1:81" ht="72" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:81" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="6" t="s">
         <v>254</v>
       </c>
@@ -10264,7 +10265,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="76" spans="1:81" ht="72" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:81" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="6" t="s">
         <v>255</v>
       </c>
@@ -10445,7 +10446,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="77" spans="1:81" ht="72" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:81" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="6" t="s">
         <v>256</v>
       </c>
@@ -10628,7 +10629,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="78" spans="1:81" ht="72" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:81" ht="72" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="6" t="s">
         <v>257</v>
       </c>
@@ -10809,7 +10810,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="79" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="6" t="s">
         <v>258</v>
       </c>
@@ -10952,7 +10953,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="80" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="6" t="s">
         <v>259</v>
       </c>
@@ -11097,7 +11098,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="81" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="6" t="s">
         <v>260</v>
       </c>
@@ -11242,7 +11243,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="82" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="6" t="s">
         <v>261</v>
       </c>
@@ -11383,7 +11384,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="83" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="6" t="s">
         <v>262</v>
       </c>
@@ -11526,7 +11527,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="84" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="6" t="s">
         <v>263</v>
       </c>
@@ -11665,7 +11666,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="85" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="6" t="s">
         <v>282</v>
       </c>
@@ -11806,7 +11807,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="86" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="6" t="s">
         <v>188</v>
       </c>
@@ -11886,7 +11887,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="87" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="6" t="s">
         <v>190</v>
       </c>
@@ -12017,7 +12018,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="88" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="6" t="s">
         <v>192</v>
       </c>
@@ -12148,7 +12149,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="89" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="6" t="s">
         <v>194</v>
       </c>
@@ -12279,7 +12280,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="90" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="6" t="s">
         <v>196</v>
       </c>
@@ -12420,7 +12421,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="91" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="6" t="s">
         <v>198</v>
       </c>
@@ -12563,7 +12564,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="92" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="6" t="s">
         <v>201</v>
       </c>
@@ -12700,7 +12701,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="93" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="6" t="s">
         <v>203</v>
       </c>
@@ -12976,7 +12977,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="95" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="6" t="s">
         <v>207</v>
       </c>
@@ -13111,7 +13112,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="96" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="6" t="s">
         <v>209</v>
       </c>
@@ -13248,7 +13249,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="97" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="6" t="s">
         <v>211</v>
       </c>
@@ -13387,7 +13388,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="98" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="6" t="s">
         <v>213</v>
       </c>
@@ -13443,7 +13444,7 @@
       </c>
       <c r="CC98" s="1"/>
     </row>
-    <row r="99" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="6" t="s">
         <v>214</v>
       </c>
@@ -13557,7 +13558,7 @@
       </c>
       <c r="CC99" s="1"/>
     </row>
-    <row r="100" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="6" t="s">
         <v>215</v>
       </c>
@@ -13671,7 +13672,7 @@
       </c>
       <c r="CC100" s="1"/>
     </row>
-    <row r="101" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="6" t="s">
         <v>216</v>
       </c>
@@ -13784,7 +13785,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="102" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="6" t="s">
         <v>217</v>
       </c>
@@ -13909,7 +13910,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="103" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" s="6" t="s">
         <v>283</v>
       </c>
@@ -14036,7 +14037,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="104" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" s="6" t="s">
         <v>218</v>
       </c>
@@ -14163,7 +14164,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="105" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" s="6" t="s">
         <v>284</v>
       </c>
@@ -14294,7 +14295,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="106" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" s="6" t="s">
         <v>219</v>
       </c>
@@ -14423,7 +14424,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="107" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" s="6" t="s">
         <v>220</v>
       </c>
@@ -14507,7 +14508,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="108" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" s="6" t="s">
         <v>97</v>
       </c>
@@ -14642,7 +14643,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="109" spans="1:81" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:81" ht="28.8" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" s="6" t="s">
         <v>98</v>
       </c>
@@ -14777,7 +14778,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="110" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" s="6" t="s">
         <v>242</v>
       </c>
@@ -14912,7 +14913,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="111" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" s="6" t="s">
         <v>243</v>
       </c>
@@ -15089,7 +15090,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="112" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" s="6" t="s">
         <v>244</v>
       </c>
@@ -15270,7 +15271,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="113" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="6" t="s">
         <v>245</v>
       </c>
@@ -15449,7 +15450,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="114" spans="1:81" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:81" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="6" t="s">
         <v>246</v>
       </c>
@@ -15632,7 +15633,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="115" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="6" t="s">
         <v>247</v>
       </c>
@@ -15813,7 +15814,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="116" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="6" t="s">
         <v>248</v>
       </c>
@@ -15956,7 +15957,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="117" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="6" t="s">
         <v>249</v>
       </c>
@@ -16101,7 +16102,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="118" spans="1:81" ht="43.2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:81" ht="43.2" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="6" t="s">
         <v>250</v>
       </c>
@@ -16240,7 +16241,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="119" spans="1:81" ht="57.6" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:81" ht="57.6" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="6" t="s">
         <v>285</v>
       </c>
@@ -16382,7 +16383,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:CC119" xr:uid="{1065429E-9165-42A9-9DDC-E545596C17BE}"/>
+  <autoFilter ref="A1:CC119" xr:uid="{1065429E-9165-42A9-9DDC-E545596C17BE}">
+    <filterColumn colId="12">
+      <filters>
+        <filter val="Y"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/ns_playwright_automation/test_data/ShippingData_NS.xlsx
+++ b/ns_playwright_automation/test_data/ShippingData_NS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\struts_playwright_automation\ns_playwright_automation\test_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9161F8F6-80E2-4033-8D3C-4E83855DA772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DC4B545-456E-4335-A8BF-4B48005BAEAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="590" xr2:uid="{82038ABE-7B8C-4146-9485-918A215A8E15}"/>
   </bookViews>
@@ -6770,7 +6770,7 @@
       </c>
       <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="N44" s="1"/>
       <c r="O44" s="1"/>
@@ -8505,7 +8505,7 @@
       </c>
       <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="N61" s="1"/>
       <c r="O61" s="1"/>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="L71" s="1"/>
       <c r="M71" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="N71" s="1" t="s">
         <v>41</v>
@@ -12870,7 +12870,7 @@
       </c>
       <c r="L94" s="1"/>
       <c r="M94" s="1" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="N94" s="1"/>
       <c r="O94" s="1"/>
